--- a/hardware/phase_1/claude_output/Sensor_Wiring_Reference.xlsx
+++ b/hardware/phase_1/claude_output/Sensor_Wiring_Reference.xlsx
@@ -3085,7 +3085,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>MDD10A_R M1A</t>
+          <t>MDD10A_R M2A</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>MDD10A_R M1B</t>
+          <t>MDD10A_R M2B</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>MDD10A_R M2A</t>
+          <t>MDD10A_R M1A</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>MDD10A_R M2B</t>
+          <t>MDD10A_R M1B</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>MDD10A_L M1A</t>
+          <t>MDD10A_L M2A</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>MDD10A_L M1B</t>
+          <t>MDD10A_L M2B</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>MDD10A_L M2A</t>
+          <t>MDD10A_L M1A</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>MDD10A_L M2B</t>
+          <t>MDD10A_L M1B</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
@@ -4188,7 +4188,7 @@
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>mtr_r_f</t>
+          <t>mtr_r_b</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
@@ -4231,7 +4231,7 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>mtr_r_f</t>
+          <t>mtr_r_b</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
@@ -4274,7 +4274,7 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>mtr_r_b</t>
+          <t>mtr_r_f</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
@@ -4317,7 +4317,7 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>mtr_r_b</t>
+          <t>mtr_r_f</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
@@ -4403,7 +4403,7 @@
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>mtr_l_f</t>
+          <t>mtr_l_b</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -4446,7 +4446,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>mtr_l_f</t>
+          <t>mtr_l_b</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
@@ -4489,7 +4489,7 @@
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>mtr_l_b</t>
+          <t>mtr_l_f</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
@@ -4532,7 +4532,7 @@
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>mtr_l_b</t>
+          <t>mtr_l_f</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Wire all four motors the SAME way physically - red to the A terminal, black to B, encoder yellow to its A pin and white to its B pin. The left-side mirror is handled in software: mtr_l_f and mtr_l_b run forward_dir=0, and the Python constants swap enc_a/enc_b for that pair. Do not swap leads or encoder wires to achieve it, or the software mirror will cancel the hardware one and the left wheels will run backwards with inverted counts.</t>
+          <t>Wire all four motors the SAME way physically - red to the A terminal, black to B, encoder yellow to its A pin and white to its B pin. The left-side mirror is handled in software: mtr_l_f and mtr_l_b run forward_dir=0, and the Python constants swap enc_a/enc_b for that pair. Do not swap leads or encoder wires to achieve it, or the software mirror will cancel the hardware one and the left wheels will run backwards with inverted counts. CHANNEL ASSIGNMENT CHANGED Oct 2026: on BOTH MDD10As the FRONT motor is on CH2 (M2A/M2B) and the REAR motor on CH1 (M1A/M1B) - the as-built motor leads after the top-deck rebuild, kept by owner decision. The Pi-to-MDD10A signal wires did not move; the PWM/DIR rows above were re-labelled to the motor each channel now drives (GPIO 18/23 = mtr_r_b, 19/24 = mtr_r_f, 12/17 = mtr_l_b, 13/27 = mtr_l_f). Found by the wheel test: GPIO 18 turned the right REAR wheel.</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>mtr_l_f DIR</t>
+          <t>mtr_l_b DIR</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>mtr_r_f PWM</t>
+          <t>mtr_r_b PWM</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>mtr_l_b DIR</t>
+          <t>mtr_l_f DIR</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>mtr_r_f DIR</t>
+          <t>mtr_r_b DIR</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>mtr_r_b DIR</t>
+          <t>mtr_r_f DIR</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>mtr_l_f PWM</t>
+          <t>mtr_l_b PWM</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>mtr_l_b PWM</t>
+          <t>mtr_l_f PWM</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>mtr_r_b PWM</t>
+          <t>mtr_r_f PWM</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -6034,6 +6034,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr"/>
     </row>
+    <row r="42"/>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="18" t="inlineStr">
         <is>
